--- a/www/flightdata/xlsx/eoss-342.xlsx
+++ b/www/flightdata/xlsx/eoss-342.xlsx
@@ -3297,7 +3297,7 @@
         <v>30852.77</v>
       </c>
       <c r="I2">
-        <v>563</v>
+        <v>413</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
